--- a/scholarship_application_forms/037_tabse_scholarship_application_form--scholarship_application_forms.xlsx
+++ b/scholarship_application_forms/037_tabse_scholarship_application_form--scholarship_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>Work Experience Start Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>Work Experience End Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Personal References Reference Job Title</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Personal References Reference Contact Info</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>personal_references_reference_note</t>
+          <t>personal_references_reference_note_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_"bachelor's",_'label':_"bachelor's"}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': "Bachelor's", 'label': "Bachelor's"}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_"master's",_'label':_"master's"}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': "Master's", 'label': "Master's"}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'doctorate',_'label':_'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Doctorate', 'label': 'Doctorate'}</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'computer_science',_'label':_'computer_science'}</t>
+          <t>computer_science</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Computer Science', 'label': 'Computer Science'}</t>
+          <t>Computer Science</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'engineering',_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Engineering', 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mathematics',_'label':_'mathematics'}</t>
+          <t>mathematics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mathematics', 'label': 'Mathematics'}</t>
+          <t>Mathematics</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'professional_reference',_'label':_'professional_reference'}</t>
+          <t>professional_reference</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Professional Reference', 'label': 'Professional Reference'}</t>
+          <t>Professional Reference</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'academic_reference',_'label':_'academic_reference'}</t>
+          <t>academic_reference</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Academic Reference', 'label': 'Academic Reference'}</t>
+          <t>Academic Reference</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'character_reference',_'label':_'character_reference'}</t>
+          <t>character_reference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Character Reference', 'label': 'Character Reference'}</t>
+          <t>Character Reference</t>
         </is>
       </c>
     </row>
